--- a/AAII_Financials/Quarterly/SSUNF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SSUNF_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -717,25 +717,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>478900</v>
+        <v>480300</v>
       </c>
       <c r="E8" s="3">
-        <v>279100</v>
+        <v>279900</v>
       </c>
       <c r="F8" s="3">
-        <v>351800</v>
+        <v>352800</v>
       </c>
       <c r="G8" s="3">
-        <v>522300</v>
+        <v>523800</v>
       </c>
       <c r="H8" s="3">
-        <v>204400</v>
+        <v>205000</v>
       </c>
       <c r="I8" s="3">
-        <v>272200</v>
+        <v>273000</v>
       </c>
       <c r="J8" s="3">
-        <v>406200</v>
+        <v>407400</v>
       </c>
       <c r="K8" s="3">
         <v>699200</v>
@@ -746,25 +746,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>377000</v>
+        <v>378100</v>
       </c>
       <c r="E9" s="3">
-        <v>202100</v>
+        <v>202700</v>
       </c>
       <c r="F9" s="3">
-        <v>226900</v>
+        <v>227500</v>
       </c>
       <c r="G9" s="3">
-        <v>330800</v>
+        <v>331800</v>
       </c>
       <c r="H9" s="3">
-        <v>130600</v>
+        <v>131000</v>
       </c>
       <c r="I9" s="3">
-        <v>161200</v>
+        <v>161700</v>
       </c>
       <c r="J9" s="3">
-        <v>250900</v>
+        <v>251600</v>
       </c>
       <c r="K9" s="3">
         <v>450200</v>
@@ -775,25 +775,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>101900</v>
+        <v>102200</v>
       </c>
       <c r="E10" s="3">
-        <v>76900</v>
+        <v>77100</v>
       </c>
       <c r="F10" s="3">
-        <v>124900</v>
+        <v>125200</v>
       </c>
       <c r="G10" s="3">
-        <v>191500</v>
+        <v>192000</v>
       </c>
       <c r="H10" s="3">
-        <v>73800</v>
+        <v>74000</v>
       </c>
       <c r="I10" s="3">
-        <v>111000</v>
+        <v>111300</v>
       </c>
       <c r="J10" s="3">
-        <v>155400</v>
+        <v>155800</v>
       </c>
       <c r="K10" s="3">
         <v>249000</v>
@@ -878,7 +878,7 @@
         <v>200</v>
       </c>
       <c r="E14" s="3">
-        <v>276600</v>
+        <v>277400</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -904,22 +904,22 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>29900</v>
+        <v>30000</v>
       </c>
       <c r="E15" s="3">
         <v>16300</v>
       </c>
       <c r="F15" s="3">
-        <v>18000</v>
+        <v>18100</v>
       </c>
       <c r="G15" s="3">
-        <v>24200</v>
+        <v>24300</v>
       </c>
       <c r="H15" s="3">
         <v>6600</v>
       </c>
       <c r="I15" s="3">
-        <v>8200</v>
+        <v>8300</v>
       </c>
       <c r="J15" s="3">
         <v>16100</v>
@@ -943,25 +943,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>662600</v>
+        <v>664500</v>
       </c>
       <c r="E17" s="3">
-        <v>614000</v>
+        <v>615800</v>
       </c>
       <c r="F17" s="3">
-        <v>406100</v>
+        <v>407300</v>
       </c>
       <c r="G17" s="3">
-        <v>762300</v>
+        <v>764500</v>
       </c>
       <c r="H17" s="3">
-        <v>225500</v>
+        <v>226100</v>
       </c>
       <c r="I17" s="3">
-        <v>277700</v>
+        <v>278400</v>
       </c>
       <c r="J17" s="3">
-        <v>412600</v>
+        <v>413800</v>
       </c>
       <c r="K17" s="3">
         <v>715200</v>
@@ -972,19 +972,19 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-183700</v>
+        <v>-184200</v>
       </c>
       <c r="E18" s="3">
-        <v>-334900</v>
+        <v>-335900</v>
       </c>
       <c r="F18" s="3">
-        <v>-54400</v>
+        <v>-54500</v>
       </c>
       <c r="G18" s="3">
-        <v>-240000</v>
+        <v>-240700</v>
       </c>
       <c r="H18" s="3">
-        <v>-21000</v>
+        <v>-21100</v>
       </c>
       <c r="I18" s="3">
         <v>-5400</v>
@@ -1043,19 +1043,19 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-154500</v>
+        <v>-154900</v>
       </c>
       <c r="E21" s="3">
-        <v>-29600</v>
+        <v>-29700</v>
       </c>
       <c r="F21" s="3">
-        <v>-46000</v>
+        <v>-46100</v>
       </c>
       <c r="G21" s="3">
-        <v>-200500</v>
+        <v>-201100</v>
       </c>
       <c r="H21" s="3">
-        <v>-8000</v>
+        <v>-8100</v>
       </c>
       <c r="I21" s="3">
         <v>-2600</v>
@@ -1072,7 +1072,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>14300</v>
+        <v>14400</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>8</v>
@@ -1101,16 +1101,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-199100</v>
+        <v>-199700</v>
       </c>
       <c r="E23" s="3">
-        <v>-322500</v>
+        <v>-323400</v>
       </c>
       <c r="F23" s="3">
-        <v>-64000</v>
+        <v>-64200</v>
       </c>
       <c r="G23" s="3">
-        <v>-227500</v>
+        <v>-228200</v>
       </c>
       <c r="H23" s="3">
         <v>-17300</v>
@@ -1133,7 +1133,7 @@
         <v>-3300</v>
       </c>
       <c r="E24" s="3">
-        <v>44700</v>
+        <v>44800</v>
       </c>
       <c r="F24" s="3">
         <v>-7200</v>
@@ -1188,16 +1188,16 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-195800</v>
+        <v>-196400</v>
       </c>
       <c r="E26" s="3">
-        <v>-367200</v>
+        <v>-368200</v>
       </c>
       <c r="F26" s="3">
-        <v>-56900</v>
+        <v>-57000</v>
       </c>
       <c r="G26" s="3">
-        <v>-218800</v>
+        <v>-219500</v>
       </c>
       <c r="H26" s="3">
         <v>-13900</v>
@@ -1206,7 +1206,7 @@
         <v>-14100</v>
       </c>
       <c r="J26" s="3">
-        <v>-13000</v>
+        <v>-13100</v>
       </c>
       <c r="K26" s="3">
         <v>-22400</v>
@@ -1217,19 +1217,19 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-196000</v>
+        <v>-196500</v>
       </c>
       <c r="E27" s="3">
-        <v>-366600</v>
+        <v>-367700</v>
       </c>
       <c r="F27" s="3">
-        <v>-57000</v>
+        <v>-57100</v>
       </c>
       <c r="G27" s="3">
-        <v>-218800</v>
+        <v>-219500</v>
       </c>
       <c r="H27" s="3">
-        <v>-13200</v>
+        <v>-13300</v>
       </c>
       <c r="I27" s="3">
         <v>-14000</v>
@@ -1278,7 +1278,7 @@
         <v>500</v>
       </c>
       <c r="E29" s="3">
-        <v>28600</v>
+        <v>28700</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>8</v>
@@ -1391,19 +1391,19 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-195400</v>
+        <v>-196000</v>
       </c>
       <c r="E33" s="3">
-        <v>-338000</v>
+        <v>-338900</v>
       </c>
       <c r="F33" s="3">
-        <v>-57000</v>
+        <v>-57100</v>
       </c>
       <c r="G33" s="3">
-        <v>-218800</v>
+        <v>-219500</v>
       </c>
       <c r="H33" s="3">
-        <v>-22200</v>
+        <v>-22300</v>
       </c>
       <c r="I33" s="3">
         <v>-14000</v>
@@ -1449,19 +1449,19 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-195400</v>
+        <v>-196000</v>
       </c>
       <c r="E35" s="3">
-        <v>-338000</v>
+        <v>-338900</v>
       </c>
       <c r="F35" s="3">
-        <v>-57000</v>
+        <v>-57100</v>
       </c>
       <c r="G35" s="3">
-        <v>-218800</v>
+        <v>-219500</v>
       </c>
       <c r="H35" s="3">
-        <v>-22200</v>
+        <v>-22300</v>
       </c>
       <c r="I35" s="3">
         <v>-14000</v>
@@ -1538,19 +1538,19 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>38400</v>
+        <v>38500</v>
       </c>
       <c r="E41" s="3">
-        <v>46700</v>
+        <v>46800</v>
       </c>
       <c r="F41" s="3">
-        <v>59900</v>
+        <v>60100</v>
       </c>
       <c r="G41" s="3">
-        <v>74400</v>
+        <v>74600</v>
       </c>
       <c r="H41" s="3">
-        <v>55000</v>
+        <v>55200</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>8</v>
@@ -1570,16 +1570,16 @@
         <v>18700</v>
       </c>
       <c r="E42" s="3">
-        <v>21800</v>
+        <v>21900</v>
       </c>
       <c r="F42" s="3">
-        <v>20500</v>
+        <v>20600</v>
       </c>
       <c r="G42" s="3">
         <v>17300</v>
       </c>
       <c r="H42" s="3">
-        <v>26000</v>
+        <v>26100</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>8</v>
@@ -1596,19 +1596,19 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>30600</v>
+        <v>30700</v>
       </c>
       <c r="E43" s="3">
-        <v>27200</v>
+        <v>27300</v>
       </c>
       <c r="F43" s="3">
-        <v>25600</v>
+        <v>25700</v>
       </c>
       <c r="G43" s="3">
         <v>27500</v>
       </c>
       <c r="H43" s="3">
-        <v>28500</v>
+        <v>28600</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>8</v>
@@ -1625,19 +1625,19 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>279300</v>
+        <v>280100</v>
       </c>
       <c r="E44" s="3">
-        <v>324400</v>
+        <v>325300</v>
       </c>
       <c r="F44" s="3">
-        <v>365100</v>
+        <v>366100</v>
       </c>
       <c r="G44" s="3">
-        <v>340400</v>
+        <v>341300</v>
       </c>
       <c r="H44" s="3">
-        <v>197400</v>
+        <v>197900</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>8</v>
@@ -1654,19 +1654,19 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>54700</v>
+        <v>54800</v>
       </c>
       <c r="E45" s="3">
-        <v>56200</v>
+        <v>56400</v>
       </c>
       <c r="F45" s="3">
-        <v>41800</v>
+        <v>41900</v>
       </c>
       <c r="G45" s="3">
-        <v>52100</v>
+        <v>52200</v>
       </c>
       <c r="H45" s="3">
-        <v>36200</v>
+        <v>36300</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>8</v>
@@ -1683,19 +1683,19 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>421600</v>
+        <v>422800</v>
       </c>
       <c r="E46" s="3">
-        <v>476300</v>
+        <v>477700</v>
       </c>
       <c r="F46" s="3">
-        <v>512900</v>
+        <v>514300</v>
       </c>
       <c r="G46" s="3">
-        <v>511600</v>
+        <v>513000</v>
       </c>
       <c r="H46" s="3">
-        <v>343200</v>
+        <v>344200</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>8</v>
@@ -1718,7 +1718,7 @@
         <v>5500</v>
       </c>
       <c r="F47" s="3">
-        <v>5600</v>
+        <v>5700</v>
       </c>
       <c r="G47" s="3">
         <v>3600</v>
@@ -1741,19 +1741,19 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>191500</v>
+        <v>192000</v>
       </c>
       <c r="E48" s="3">
-        <v>204100</v>
+        <v>204700</v>
       </c>
       <c r="F48" s="3">
-        <v>144400</v>
+        <v>144800</v>
       </c>
       <c r="G48" s="3">
-        <v>149400</v>
+        <v>149800</v>
       </c>
       <c r="H48" s="3">
-        <v>106700</v>
+        <v>107000</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>8</v>
@@ -1770,19 +1770,19 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>731800</v>
+        <v>733900</v>
       </c>
       <c r="E49" s="3">
-        <v>734900</v>
+        <v>737000</v>
       </c>
       <c r="F49" s="3">
-        <v>1008000</v>
+        <v>1010800</v>
       </c>
       <c r="G49" s="3">
-        <v>1014700</v>
+        <v>1017600</v>
       </c>
       <c r="H49" s="3">
-        <v>354600</v>
+        <v>355600</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>8</v>
@@ -1915,19 +1915,19 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1355100</v>
+        <v>1358900</v>
       </c>
       <c r="E54" s="3">
-        <v>1420800</v>
+        <v>1424900</v>
       </c>
       <c r="F54" s="3">
-        <v>1671000</v>
+        <v>1675800</v>
       </c>
       <c r="G54" s="3">
-        <v>1679300</v>
+        <v>1684100</v>
       </c>
       <c r="H54" s="3">
-        <v>806000</v>
+        <v>808300</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>8</v>
@@ -1970,19 +1970,19 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>178300</v>
+        <v>178800</v>
       </c>
       <c r="E57" s="3">
-        <v>211500</v>
+        <v>212100</v>
       </c>
       <c r="F57" s="3">
-        <v>193600</v>
+        <v>194100</v>
       </c>
       <c r="G57" s="3">
-        <v>166300</v>
+        <v>166800</v>
       </c>
       <c r="H57" s="3">
-        <v>111400</v>
+        <v>111700</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>8</v>
@@ -1999,16 +1999,16 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>28000</v>
+        <v>28100</v>
       </c>
       <c r="E58" s="3">
-        <v>46000</v>
+        <v>46100</v>
       </c>
       <c r="F58" s="3">
-        <v>44700</v>
+        <v>44800</v>
       </c>
       <c r="G58" s="3">
-        <v>168100</v>
+        <v>168500</v>
       </c>
       <c r="H58" s="3">
         <v>30100</v>
@@ -2028,19 +2028,19 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>104600</v>
+        <v>104900</v>
       </c>
       <c r="E59" s="3">
-        <v>93100</v>
+        <v>93400</v>
       </c>
       <c r="F59" s="3">
-        <v>94500</v>
+        <v>94800</v>
       </c>
       <c r="G59" s="3">
-        <v>91200</v>
+        <v>91500</v>
       </c>
       <c r="H59" s="3">
-        <v>62400</v>
+        <v>62600</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>8</v>
@@ -2057,19 +2057,19 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>310900</v>
+        <v>311700</v>
       </c>
       <c r="E60" s="3">
-        <v>350600</v>
+        <v>351600</v>
       </c>
       <c r="F60" s="3">
-        <v>332800</v>
+        <v>333700</v>
       </c>
       <c r="G60" s="3">
-        <v>425600</v>
+        <v>426900</v>
       </c>
       <c r="H60" s="3">
-        <v>203900</v>
+        <v>204500</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>8</v>
@@ -2086,19 +2086,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>352000</v>
+        <v>353000</v>
       </c>
       <c r="E61" s="3">
-        <v>344200</v>
+        <v>345100</v>
       </c>
       <c r="F61" s="3">
-        <v>262900</v>
+        <v>263600</v>
       </c>
       <c r="G61" s="3">
-        <v>114500</v>
+        <v>114800</v>
       </c>
       <c r="H61" s="3">
-        <v>152300</v>
+        <v>152800</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2115,19 +2115,19 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>213100</v>
+        <v>213700</v>
       </c>
       <c r="E62" s="3">
-        <v>56300</v>
+        <v>56500</v>
       </c>
       <c r="F62" s="3">
-        <v>67600</v>
+        <v>67800</v>
       </c>
       <c r="G62" s="3">
-        <v>84300</v>
+        <v>84500</v>
       </c>
       <c r="H62" s="3">
-        <v>44700</v>
+        <v>44800</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>8</v>
@@ -2231,19 +2231,19 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>875900</v>
+        <v>878400</v>
       </c>
       <c r="E66" s="3">
-        <v>751000</v>
+        <v>753200</v>
       </c>
       <c r="F66" s="3">
-        <v>663300</v>
+        <v>665200</v>
       </c>
       <c r="G66" s="3">
-        <v>624400</v>
+        <v>626200</v>
       </c>
       <c r="H66" s="3">
-        <v>400900</v>
+        <v>402100</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>8</v>
@@ -2389,19 +2389,19 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>428700</v>
+        <v>429900</v>
       </c>
       <c r="E72" s="3">
-        <v>619300</v>
+        <v>621100</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G72" s="3">
-        <v>1004500</v>
+        <v>1007400</v>
       </c>
       <c r="H72" s="3">
-        <v>382000</v>
+        <v>383100</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>8</v>
@@ -2505,19 +2505,19 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>479100</v>
+        <v>480500</v>
       </c>
       <c r="E76" s="3">
-        <v>669800</v>
+        <v>671700</v>
       </c>
       <c r="F76" s="3">
-        <v>1007700</v>
+        <v>1010600</v>
       </c>
       <c r="G76" s="3">
-        <v>1054800</v>
+        <v>1057900</v>
       </c>
       <c r="H76" s="3">
-        <v>405100</v>
+        <v>406300</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>8</v>
@@ -2597,19 +2597,19 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-195400</v>
+        <v>-196000</v>
       </c>
       <c r="E81" s="3">
-        <v>-338000</v>
+        <v>-338900</v>
       </c>
       <c r="F81" s="3">
-        <v>-57000</v>
+        <v>-57100</v>
       </c>
       <c r="G81" s="3">
-        <v>-218800</v>
+        <v>-219500</v>
       </c>
       <c r="H81" s="3">
-        <v>-22200</v>
+        <v>-22300</v>
       </c>
       <c r="I81" s="3">
         <v>-14000</v>
@@ -2639,22 +2639,22 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>30300</v>
+        <v>30400</v>
       </c>
       <c r="E83" s="3">
-        <v>292800</v>
+        <v>293700</v>
       </c>
       <c r="F83" s="3">
-        <v>18000</v>
+        <v>18100</v>
       </c>
       <c r="G83" s="3">
-        <v>24200</v>
+        <v>24300</v>
       </c>
       <c r="H83" s="3">
         <v>9200</v>
       </c>
       <c r="I83" s="3">
-        <v>8200</v>
+        <v>8300</v>
       </c>
       <c r="J83" s="3">
         <v>16100</v>
@@ -2813,19 +2813,19 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-146500</v>
+        <v>-146900</v>
       </c>
       <c r="E89" s="3">
-        <v>-16900</v>
+        <v>-17000</v>
       </c>
       <c r="F89" s="3">
-        <v>-29200</v>
+        <v>-29300</v>
       </c>
       <c r="G89" s="3">
-        <v>-160600</v>
+        <v>-161000</v>
       </c>
       <c r="H89" s="3">
-        <v>-19400</v>
+        <v>-19500</v>
       </c>
       <c r="I89" s="3">
         <v>-8800</v>
@@ -2942,25 +2942,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-18100</v>
+        <v>-18200</v>
       </c>
       <c r="E94" s="3">
-        <v>-28100</v>
+        <v>-28200</v>
       </c>
       <c r="F94" s="3">
-        <v>-23400</v>
+        <v>-23500</v>
       </c>
       <c r="G94" s="3">
-        <v>-206800</v>
+        <v>-207400</v>
       </c>
       <c r="H94" s="3">
-        <v>-10600</v>
+        <v>-10700</v>
       </c>
       <c r="I94" s="3">
-        <v>-11700</v>
+        <v>-11800</v>
       </c>
       <c r="J94" s="3">
-        <v>-11900</v>
+        <v>-12000</v>
       </c>
       <c r="K94" s="3">
         <v>-30400</v>
@@ -3100,25 +3100,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>156900</v>
+        <v>157300</v>
       </c>
       <c r="E100" s="3">
-        <v>34200</v>
+        <v>34300</v>
       </c>
       <c r="F100" s="3">
-        <v>37900</v>
+        <v>38000</v>
       </c>
       <c r="G100" s="3">
-        <v>386700</v>
+        <v>387800</v>
       </c>
       <c r="H100" s="3">
-        <v>19500</v>
+        <v>19600</v>
       </c>
       <c r="I100" s="3">
-        <v>28600</v>
+        <v>28700</v>
       </c>
       <c r="J100" s="3">
-        <v>-29600</v>
+        <v>-29700</v>
       </c>
       <c r="K100" s="3">
         <v>21400</v>
@@ -3158,25 +3158,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-8100</v>
+        <v>-8200</v>
       </c>
       <c r="E102" s="3">
-        <v>-13200</v>
+        <v>-13300</v>
       </c>
       <c r="F102" s="3">
-        <v>-14400</v>
+        <v>-14500</v>
       </c>
       <c r="G102" s="3">
-        <v>19300</v>
+        <v>19400</v>
       </c>
       <c r="H102" s="3">
-        <v>-10500</v>
+        <v>-10600</v>
       </c>
       <c r="I102" s="3">
-        <v>8100</v>
+        <v>8200</v>
       </c>
       <c r="J102" s="3">
-        <v>-46200</v>
+        <v>-46400</v>
       </c>
       <c r="K102" s="3">
         <v>-13600</v>
